--- a/outputs/evaluation/decision/v2/CF_M01/CF_M01_decision_eval_avg.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M01/CF_M01_decision_eval_avg.xlsx
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7936</v>
+        <v>0.7857</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7619</v>
+        <v>0.7143</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8509</v>
+        <v>0.8963</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5917</v>
+        <v>0.6198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7111</v>
+        <v>0.7389</v>
       </c>
       <c r="D7" t="n">
-        <v>0.944</v>
+        <v>0.9621</v>
       </c>
     </row>
     <row r="8">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6667</v>
+        <v>6.3333</v>
       </c>
     </row>
     <row r="4">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3333</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.6667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7936</v>
+        <v>0.7857</v>
       </c>
     </row>
     <row r="8">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7619</v>
+        <v>0.7143</v>
       </c>
     </row>
     <row r="9">
